--- a/data/trans_orig/IQ17A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ17A-Clase-trans_orig.xlsx
@@ -958,7 +958,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>2405</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3255</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2593</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>2723</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>2494</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15898</t>
+          <t>15436</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21560</t>
+          <t>21529</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39712</t>
+          <t>39677</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43413</t>
+          <t>43410</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1593,12 +1593,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -2402,12 +2402,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>602</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5171</t>
+          <t>4889</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2417,12 +2417,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>635</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5981</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17784</t>
+          <t>18066</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22365</t>
+          <t>22353</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14026</t>
+          <t>14158</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>35491</t>
+          <t>35348</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41378</t>
+          <t>41401</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t>3764</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3668</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6316</t>
+          <t>6954</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3457,12 +3457,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7593</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>26,92%</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7259</t>
+          <t>7184</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11881</t>
+          <t>11778</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17988</t>
+          <t>17384</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3568,12 +3568,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>21014</t>
+          <t>21012</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>27772</t>
+          <t>27743</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,05%</t>
         </is>
       </c>
     </row>
@@ -4336,12 +4336,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>680</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>5476</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>683</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>5814</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4386,12 +4386,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -4412,12 +4412,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2413</t>
+          <t>2136</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>9618</t>
+          <t>8927</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4427,12 +4427,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>7025</t>
+          <t>7158</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4462,12 +4462,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>13799</t>
+          <t>13269</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -4523,12 +4523,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>28397</t>
+          <t>29088</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>35602</t>
+          <t>35879</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>39102</t>
+          <t>39301</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>46284</t>
+          <t>46485</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>70980</t>
+          <t>71410</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>81074</t>
+          <t>80902</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>92,99%</t>
         </is>
       </c>
     </row>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>4353</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>3976</t>
+          <t>3799</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -5417,12 +5417,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>451</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5487,12 +5487,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>7027</t>
+          <t>6485</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5502,12 +5502,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>15,61%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>15559</t>
+          <t>16018</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>19687</t>
+          <t>19686</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>15523</t>
+          <t>15705</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>20731</t>
+          <t>20725</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>32993</t>
+          <t>33558</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>39691</t>
+          <t>39746</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,65%</t>
         </is>
       </c>
     </row>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3328</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3940</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>2661</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>13554</t>
+          <t>13952</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>24617</t>
+          <t>24678</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3623</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>4138</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -7245,7 +7245,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>3903</t>
+          <t>4599</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>9246</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>9230</t>
+          <t>8336</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -7427,12 +7427,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>5554</t>
+          <t>5592</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>15164</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7442,12 +7442,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>15270</t>
+          <t>15494</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7497,12 +7497,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>13171</t>
+          <t>13600</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>27098</t>
+          <t>26780</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -7538,12 +7538,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>105802</t>
+          <t>105020</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>115141</t>
+          <t>114899</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7553,12 +7553,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>129154</t>
+          <t>129911</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>142045</t>
+          <t>142136</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>239297</t>
+          <t>238199</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>254540</t>
+          <t>254229</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7623,12 +7623,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,94%</t>
         </is>
       </c>
     </row>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>4289</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3743</t>
+          <t>3701</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>677</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -8666,12 +8666,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>710</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6563</t>
+          <t>6461</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8681,12 +8681,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8701,12 +8701,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>681</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6566</t>
+          <t>6392</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8716,12 +8716,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2162</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9608</t>
+          <t>10057</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8751,12 +8751,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,87%</t>
         </is>
       </c>
     </row>
@@ -8777,12 +8777,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14831</t>
+          <t>14941</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21245</t>
+          <t>20862</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8812,12 +8812,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13954</t>
+          <t>13988</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20282</t>
+          <t>20318</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31955</t>
+          <t>31211</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>40287</t>
+          <t>40136</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,27%</t>
         </is>
       </c>
     </row>
@@ -9560,12 +9560,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>561</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4526</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9630,12 +9630,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>561</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>5486</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,47%</t>
         </is>
       </c>
     </row>
@@ -9671,12 +9671,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>611</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>5370</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9741,12 +9741,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>608</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>5481</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9761,7 +9761,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -9782,12 +9782,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17431</t>
+          <t>16920</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22878</t>
+          <t>22992</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9797,12 +9797,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9852,12 +9852,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32248</t>
+          <t>32636</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>38916</t>
+          <t>39315</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>96,55%</t>
         </is>
       </c>
     </row>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10529,7 +10529,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>3675</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10544,7 +10544,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3248</t>
+          <t>3464</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10585,7 +10585,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10640,7 +10640,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -10711,12 +10711,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>599</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5310</t>
+          <t>5788</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10726,12 +10726,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>602</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5866</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -10787,7 +10787,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17011</t>
+          <t>16795</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -10822,12 +10822,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12903</t>
+          <t>12641</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>18354</t>
+          <t>18341</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10837,12 +10837,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10857,12 +10857,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>32124</t>
+          <t>31909</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>38084</t>
+          <t>38013</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -11242,7 +11242,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2746</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>2792</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -11570,12 +11570,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>575</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6053</t>
+          <t>6020</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -11585,12 +11585,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7280</t>
+          <t>6245</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -11620,12 +11620,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -11640,12 +11640,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9649</t>
+          <t>9836</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -11655,12 +11655,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -11681,12 +11681,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>7759</t>
+          <t>7051</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -11696,12 +11696,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -11716,12 +11716,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>4878</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>13937</t>
+          <t>13626</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -11731,12 +11731,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -11751,12 +11751,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>7452</t>
+          <t>7816</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>18291</t>
+          <t>18215</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -11792,12 +11792,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>34970</t>
+          <t>35459</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>42876</t>
+          <t>43018</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11827,12 +11827,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>40833</t>
+          <t>41139</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>50772</t>
+          <t>51208</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11862,12 +11862,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>79937</t>
+          <t>79526</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>92313</t>
+          <t>92156</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11877,12 +11877,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,49%</t>
         </is>
       </c>
     </row>
@@ -12504,7 +12504,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>2899</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -12519,7 +12519,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3787</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -12554,7 +12554,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -12615,7 +12615,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -12650,7 +12650,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>4381</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -12665,7 +12665,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -12686,12 +12686,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2334</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>10031</t>
+          <t>9673</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -12701,12 +12701,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -12721,12 +12721,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>9977</t>
+          <t>10028</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -12736,12 +12736,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -12756,12 +12756,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>6391</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>16549</t>
+          <t>16777</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -12797,12 +12797,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>22562</t>
+          <t>22920</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>30259</t>
+          <t>30287</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12812,12 +12812,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12832,12 +12832,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>17418</t>
+          <t>17081</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>24831</t>
+          <t>25119</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12847,12 +12847,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12867,12 +12867,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>43367</t>
+          <t>42589</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>53819</t>
+          <t>53312</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12882,12 +12882,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>86,32%</t>
         </is>
       </c>
     </row>
@@ -13696,7 +13696,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>3631</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -13711,7 +13711,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -13726,12 +13726,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>7171</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -13741,12 +13741,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -13761,12 +13761,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>2589</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>9205</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>34,79%</t>
         </is>
       </c>
     </row>
@@ -13802,7 +13802,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -13817,7 +13817,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -13837,12 +13837,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>9820</t>
+          <t>9662</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>15496</t>
+          <t>15068</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13852,12 +13852,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13872,12 +13872,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>17252</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>23990</t>
+          <t>23868</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13887,12 +13887,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,21%</t>
         </is>
       </c>
     </row>
@@ -14257,7 +14257,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -14272,7 +14272,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -14327,7 +14327,7 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -14342,7 +14342,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -14514,7 +14514,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>5019</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -14529,7 +14529,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>4554</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -14564,7 +14564,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -14585,12 +14585,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>2729</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>10931</t>
+          <t>11061</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -14600,12 +14600,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -14620,12 +14620,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>9347</t>
+          <t>9489</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -14635,12 +14635,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -14655,12 +14655,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>5987</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>16925</t>
+          <t>17209</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -14670,12 +14670,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -14696,12 +14696,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>9696</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>22128</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -14711,12 +14711,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -14731,12 +14731,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>16029</t>
+          <t>16269</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>29621</t>
+          <t>30620</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -14746,12 +14746,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -14766,12 +14766,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>29079</t>
+          <t>28823</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>48050</t>
+          <t>49113</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -14781,12 +14781,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -14807,12 +14807,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>126566</t>
+          <t>126821</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>141248</t>
+          <t>140577</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -14822,12 +14822,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -14842,12 +14842,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>123331</t>
+          <t>122893</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>139066</t>
+          <t>139293</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -14857,12 +14857,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -14877,12 +14877,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>254221</t>
+          <t>254183</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>275815</t>
+          <t>276100</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -14892,12 +14892,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,27%</t>
         </is>
       </c>
     </row>
@@ -15940,7 +15940,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -15970,12 +15970,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>585</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>5435</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -15985,12 +15985,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -16005,12 +16005,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>7469</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -16020,12 +16020,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -16046,7 +16046,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14530</t>
+          <t>14829</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -16061,7 +16061,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -16081,12 +16081,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17793</t>
+          <t>18393</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23239</t>
+          <t>23243</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -16096,12 +16096,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -16116,12 +16116,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35681</t>
+          <t>35210</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>41523</t>
+          <t>41458</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -16131,12 +16131,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -16945,7 +16945,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -16960,7 +16960,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -16980,7 +16980,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4561</t>
+          <t>4816</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -16995,7 +16995,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -17010,12 +17010,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>771</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6447</t>
+          <t>7041</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -17025,12 +17025,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
@@ -17051,7 +17051,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12454</t>
+          <t>12717</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -17066,7 +17066,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -17086,7 +17086,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18074</t>
+          <t>17819</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -17101,7 +17101,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -17121,12 +17121,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32924</t>
+          <t>32330</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>38683</t>
+          <t>38600</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -17136,12 +17136,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -17950,7 +17950,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>3080</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -17965,7 +17965,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -17985,7 +17985,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -18000,7 +18000,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -18020,7 +18020,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -18035,7 +18035,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,44%</t>
         </is>
       </c>
     </row>
@@ -18056,7 +18056,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6923</t>
+          <t>6825</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -18071,7 +18071,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -18091,7 +18091,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6320</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -18106,7 +18106,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -18126,7 +18126,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>15124</t>
+          <t>15024</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -18141,7 +18141,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -18950,12 +18950,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2548</t>
+          <t>2525</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>9572</t>
+          <t>9567</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -18965,12 +18965,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -18985,12 +18985,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>7804</t>
+          <t>7894</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -19000,12 +19000,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -19020,12 +19020,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4889</t>
+          <t>4998</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>14022</t>
+          <t>14086</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -19035,12 +19035,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -19061,12 +19061,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>40941</t>
+          <t>40946</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>47965</t>
+          <t>47988</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -19076,12 +19076,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -19096,12 +19096,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>35578</t>
+          <t>35488</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>42073</t>
+          <t>42039</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -19111,12 +19111,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -19131,12 +19131,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>79874</t>
+          <t>79810</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>89007</t>
+          <t>88898</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -19146,12 +19146,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,68%</t>
         </is>
       </c>
     </row>
@@ -19405,7 +19405,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -19420,7 +19420,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -19475,7 +19475,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>2962</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -19490,7 +19490,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -19627,7 +19627,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -19697,7 +19697,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>2752</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -19712,7 +19712,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>2948</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -19753,7 +19753,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -19773,7 +19773,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>4674</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -19788,7 +19788,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -19808,7 +19808,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -19823,7 +19823,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -19899,7 +19899,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -19919,7 +19919,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -19934,7 +19934,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -19955,12 +19955,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>8409</t>
+          <t>7989</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -19970,12 +19970,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -19990,12 +19990,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>570</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -20005,12 +20005,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -20025,12 +20025,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>11471</t>
+          <t>11308</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -20040,12 +20040,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -20066,12 +20066,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>16994</t>
+          <t>17176</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>24158</t>
+          <t>24218</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -20081,12 +20081,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -20101,12 +20101,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>20735</t>
+          <t>20736</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>26767</t>
+          <t>26827</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -20116,12 +20116,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -20136,12 +20136,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>40105</t>
+          <t>41169</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>49998</t>
+          <t>50169</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -20151,12 +20151,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,54%</t>
         </is>
       </c>
     </row>
@@ -20854,7 +20854,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2598</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -20869,7 +20869,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -20924,7 +20924,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -20939,7 +20939,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>14,67%</t>
         </is>
       </c>
     </row>
@@ -20965,7 +20965,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>3535</t>
+          <t>4072</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -20980,7 +20980,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -21000,7 +21000,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -21030,12 +21030,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>651</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>5642</t>
+          <t>5817</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -21045,12 +21045,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>27,09%</t>
         </is>
       </c>
     </row>
@@ -21071,12 +21071,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>6484</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>10431</t>
+          <t>10445</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -21086,12 +21086,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>6609</t>
+          <t>6593</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -21121,7 +21121,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>15162</t>
+          <t>14974</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>20243</t>
+          <t>20261</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -21156,12 +21156,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -21415,7 +21415,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2924</t>
+          <t>2956</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -21430,7 +21430,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -21485,7 +21485,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>2384</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -21500,7 +21500,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -21637,7 +21637,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2848</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -21652,7 +21652,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -21707,7 +21707,7 @@
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -21722,7 +21722,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -21748,7 +21748,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -21763,7 +21763,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -21783,7 +21783,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -21818,7 +21818,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -21833,7 +21833,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -21859,7 +21859,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3705</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -21874,7 +21874,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -21894,7 +21894,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>4562</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -21909,7 +21909,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -21929,7 +21929,7 @@
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>5153</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -21944,7 +21944,7 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -21965,12 +21965,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>8599</t>
+          <t>8965</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>20701</t>
+          <t>19965</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -21980,12 +21980,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -22000,12 +22000,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>7119</t>
+          <t>7214</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>17788</t>
+          <t>17588</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -22015,12 +22015,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -22035,12 +22035,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>18578</t>
+          <t>18856</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>33190</t>
+          <t>34296</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -22050,12 +22050,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -22076,12 +22076,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>111251</t>
+          <t>111699</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>123699</t>
+          <t>123644</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -22091,12 +22091,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -22111,12 +22111,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>118391</t>
+          <t>118420</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>129434</t>
+          <t>129153</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -22126,12 +22126,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -22146,12 +22146,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>234410</t>
+          <t>233624</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>249936</t>
+          <t>249706</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -22161,12 +22161,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,82%</t>
         </is>
       </c>
     </row>
@@ -23133,7 +23133,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>3760</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -23148,7 +23148,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -23168,7 +23168,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>2779</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -23183,7 +23183,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -23209,7 +23209,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -23224,7 +23224,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -23244,7 +23244,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -23259,7 +23259,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -23274,12 +23274,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>406</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5156</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -23294,7 +23294,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -23315,7 +23315,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22583</t>
+          <t>22533</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -23330,7 +23330,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -23350,12 +23350,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15662</t>
+          <t>14886</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20053</t>
+          <t>20048</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -23365,12 +23365,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -23385,12 +23385,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39624</t>
+          <t>39705</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44738</t>
+          <t>44648</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -23400,12 +23400,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -23583,7 +23583,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4181</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -23598,7 +23598,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -23618,7 +23618,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>4818</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -23633,7 +23633,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -24214,7 +24214,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2955</t>
+          <t>2427</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -24229,7 +24229,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -24244,12 +24244,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>471</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7227</t>
+          <t>7015</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -24259,12 +24259,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -24279,12 +24279,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>885</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8172</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -24294,12 +24294,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,2%</t>
         </is>
       </c>
     </row>
@@ -24320,7 +24320,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7536</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -24335,7 +24335,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -24355,12 +24355,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8297</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15126</t>
+          <t>15119</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -24370,12 +24370,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -24390,12 +24390,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17314</t>
+          <t>17563</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25289</t>
+          <t>25130</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -24405,12 +24405,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,16%</t>
         </is>
       </c>
     </row>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5617</t>
+          <t>5308</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -25830,7 +25830,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -25850,7 +25850,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>6162</t>
+          <t>7591</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -25865,7 +25865,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -25891,7 +25891,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3847</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -25906,7 +25906,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -25926,7 +25926,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -25941,7 +25941,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -25961,7 +25961,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -25976,7 +25976,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -26002,7 +26002,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -26017,44 +26017,44 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
+          <t>10,95%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>1014</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>5453</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
           <t>13,26%</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>1014</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>5879</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>14,29%</t>
-        </is>
-      </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>2</t>
@@ -26072,7 +26072,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>5633</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -26087,7 +26087,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -26148,7 +26148,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -26163,7 +26163,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -26183,7 +26183,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -26198,7 +26198,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -26219,12 +26219,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>374</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -26234,12 +26234,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -26254,12 +26254,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>364</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -26269,12 +26269,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -26289,12 +26289,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6487</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -26304,12 +26304,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -26330,12 +26330,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>22995</t>
+          <t>22759</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>29027</t>
+          <t>29115</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -26345,12 +26345,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -26365,12 +26365,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>31827</t>
+          <t>32263</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>39242</t>
+          <t>39313</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -26380,12 +26380,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -26400,12 +26400,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>57783</t>
+          <t>58088</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>67019</t>
+          <t>67134</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -26415,12 +26415,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>
@@ -27153,7 +27153,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3782</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -27168,7 +27168,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -27188,7 +27188,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -27203,7 +27203,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -27229,7 +27229,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -27264,7 +27264,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>5408</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -27279,7 +27279,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -27294,12 +27294,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>595</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -27309,12 +27309,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -27335,7 +27335,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>16503</t>
+          <t>16475</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -27350,7 +27350,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -27370,12 +27370,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>24155</t>
+          <t>23733</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>29355</t>
+          <t>29346</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -27385,12 +27385,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -27405,12 +27405,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>43197</t>
+          <t>42922</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>48894</t>
+          <t>48998</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -27420,12 +27420,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -28234,7 +28234,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>4428</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -28249,7 +28249,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -28304,7 +28304,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -28319,7 +28319,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -28340,7 +28340,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>4718</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -28355,7 +28355,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -28410,7 +28410,7 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>15199</t>
+          <t>15739</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
@@ -28425,7 +28425,7 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -28608,7 +28608,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>5380</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -28623,7 +28623,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -28643,7 +28643,7 @@
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>5641</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -28658,7 +28658,7 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -28830,7 +28830,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>6172</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -28845,7 +28845,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -28865,7 +28865,7 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>7398</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -28880,7 +28880,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -28906,7 +28906,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>3721</t>
+          <t>4418</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -28921,7 +28921,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -28941,7 +28941,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>2457</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -28956,7 +28956,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -28976,7 +28976,7 @@
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>4466</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -28991,7 +28991,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -29017,7 +29017,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>4518</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -29032,7 +29032,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -29052,7 +29052,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>6100</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -29067,7 +29067,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -29087,7 +29087,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>6400</t>
+          <t>6758</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -29102,7 +29102,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -29158,47 +29158,47 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
+          <t>537</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>4977</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>4636</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="P63" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="Q63" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R63" s="2" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="S63" s="2" t="inlineStr">
-        <is>
-          <t>517</t>
-        </is>
-      </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>4804</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -29213,7 +29213,7 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -29234,12 +29234,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>11009</t>
+          <t>10438</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -29249,12 +29249,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -29269,12 +29269,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>3270</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>13241</t>
+          <t>12949</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -29284,12 +29284,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -29304,12 +29304,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>7676</t>
+          <t>7718</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>19613</t>
+          <t>19582</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -29319,12 +29319,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -29345,12 +29345,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>86141</t>
+          <t>86234</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>94915</t>
+          <t>94754</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -29360,12 +29360,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -29380,12 +29380,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>110253</t>
+          <t>110435</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>122782</t>
+          <t>122806</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -29395,12 +29395,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -29415,12 +29415,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>200396</t>
+          <t>200484</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>215822</t>
+          <t>215425</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -29430,12 +29430,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,05%</t>
         </is>
       </c>
     </row>
